--- a/TDD_examples/CASE_3_HTS_HVDC/conductor_grid.xlsx
+++ b/TDD_examples/CASE_3_HTS_HVDC/conductor_grid.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GRID" sheetId="1" r:id="Rb4459612d9b24990"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GRID" sheetId="1" r:id="R5aaa71d142434e6a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,9 +20,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">ITYMSH</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">flag for mesh type: 0 = fixed and uniform; 1 = fixed refined; 3 = adapted with initial refinement; - 1 from file; in this case the z coordinates of the conductor components must be exactly the same for each conudctor component objets.                                                                     </x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">NELREF</x:t>
@@ -538,8 +535,8 @@
       <x:c r="C5" s="34" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="36" t="s">
-        <x:v>4</x:v>
+      <x:c r="D5" s="36" t="str">
+        <x:v>Flag used to select the mesh type: 0 = fixed and uniform; 1 = fixed and refined; 3 = adaptive with initial refinement; -1 = read from file. In the latter case, the z coordinates must be identical for all conductor components.</x:v>
       </x:c>
       <x:c r="E5" s="35" t="n">
         <x:v>0</x:v>
@@ -547,7 +544,7 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="33" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="34" t="s">
         <x:v>1</x:v>
@@ -556,7 +553,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="36" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="35" t="n">
         <x:v>0</x:v>
@@ -564,16 +561,16 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="33" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="34" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B7" s="34" t="s">
+      <x:c r="C7" s="34" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C7" s="34" t="s">
+      <x:c r="D7" s="36" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="D7" s="36" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="37" t="n">
         <x:v>26</x:v>
@@ -581,16 +578,16 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="33" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B8" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D8" s="36" t="s">
         <x:v>11</x:v>
-      </x:c>
-      <x:c r="B8" s="34" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="34" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D8" s="36" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="E8" s="37" t="n">
         <x:v>33</x:v>
@@ -598,16 +595,16 @@
     </x:row>
     <x:row r="9" ht="24" hidden="0" customHeight="1">
       <x:c r="A9" s="33" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B9" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D9" s="36" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="B9" s="34" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="34" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="36" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="37" t="n">
         <x:v>0.5</x:v>
@@ -615,16 +612,16 @@
     </x:row>
     <x:row r="10" ht="24" hidden="0" customHeight="1">
       <x:c r="A10" s="33" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B10" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C10" s="34" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D10" s="36" t="s">
         <x:v>15</x:v>
-      </x:c>
-      <x:c r="B10" s="34" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="34" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D10" s="36" t="s">
-        <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="37" t="n">
         <x:v>2</x:v>
@@ -632,16 +629,16 @@
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="33" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B11" s="34" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="34" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D11" s="36" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B11" s="34" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="34" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="36" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="E11" s="37" t="n">
         <x:v>1.2</x:v>
@@ -649,16 +646,16 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="33" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B12" s="34" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="34" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D12" s="36" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="B12" s="34" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="34" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D12" s="36" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="E12" s="37" t="n">
         <x:v>1.2</x:v>
@@ -666,7 +663,7 @@
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="33" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B13" s="34" t="s">
         <x:v>1</x:v>
@@ -675,7 +672,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D13" s="36" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E13" s="34" t="n">
         <x:v>10001</x:v>
